--- a/Riscos/Riscos-modelo.xlsx
+++ b/Riscos/Riscos-modelo.xlsx
@@ -931,7 +931,7 @@
     <t xml:space="preserve">Perda de insumos e risco para a saúde do cliente</t>
   </si>
   <si>
-    <t xml:space="preserve">Fazer a manutenção preventiva a cada seis meses e instalar alarme de temperatura.</t>
+    <t xml:space="preserve">Fazer a manutenção preventiva a cada três meses.</t>
   </si>
   <si>
     <t xml:space="preserve">Pizzaiolo líder</t>
@@ -970,7 +970,7 @@
     <t xml:space="preserve">Dano à pessoa e entregas interrompidas</t>
   </si>
   <si>
-    <t xml:space="preserve">Revisar as motos todo mês, treinar direção segura e contratar seguro.</t>
+    <t xml:space="preserve">Revisar as motos todo mês e treinar direção segura. O seguro, contratado junto, compartilha o custo do acidente.</t>
   </si>
   <si>
     <t xml:space="preserve">R6</t>
@@ -1144,7 +1144,7 @@
     <t xml:space="preserve">Perda financeira e dano à imagem</t>
   </si>
   <si>
-    <t xml:space="preserve">As três cotações e as alçadas já reduzem a probabilidade ao mínimo. A auditoria confere o controle.</t>
+    <t xml:space="preserve">As três cotações e as alçadas já reduzem a probabilidade ao mínimo. A auditoria confere o controle. Contingência: se aparecer um favorecimento, suspender as compras do fornecedor e levar o caso à direção.</t>
   </si>
   <si>
     <t xml:space="preserve">C7</t>
@@ -2035,11 +2035,11 @@
         </c:ser>
         <c:gapWidth val="80"/>
         <c:overlap val="-10"/>
-        <c:axId val="13244731"/>
-        <c:axId val="34763985"/>
+        <c:axId val="44554071"/>
+        <c:axId val="25245701"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="13244731"/>
+        <c:axId val="44554071"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2071,7 +2071,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="34763985"/>
+        <c:crossAx val="25245701"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -2079,7 +2079,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="34763985"/>
+        <c:axId val="25245701"/>
         <c:scaling>
           <c:orientation val="minMax"/>
           <c:min val="0"/>
@@ -2119,7 +2119,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="13244731"/>
+        <c:crossAx val="44554071"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
         <c:majorUnit val="1"/>
@@ -2373,11 +2373,11 @@
         </c:ser>
         <c:gapWidth val="80"/>
         <c:overlap val="-10"/>
-        <c:axId val="4870605"/>
-        <c:axId val="83246300"/>
+        <c:axId val="80459992"/>
+        <c:axId val="39568036"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="4870605"/>
+        <c:axId val="80459992"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2409,7 +2409,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="83246300"/>
+        <c:crossAx val="39568036"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -2417,7 +2417,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="83246300"/>
+        <c:axId val="39568036"/>
         <c:scaling>
           <c:orientation val="minMax"/>
           <c:min val="0"/>
@@ -2457,7 +2457,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="4870605"/>
+        <c:crossAx val="80459992"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
         <c:majorUnit val="1"/>
@@ -2711,11 +2711,11 @@
         </c:ser>
         <c:gapWidth val="80"/>
         <c:overlap val="-10"/>
-        <c:axId val="10978621"/>
-        <c:axId val="40421576"/>
+        <c:axId val="42353931"/>
+        <c:axId val="95704635"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="10978621"/>
+        <c:axId val="42353931"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2747,7 +2747,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="40421576"/>
+        <c:crossAx val="95704635"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -2755,7 +2755,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="40421576"/>
+        <c:axId val="95704635"/>
         <c:scaling>
           <c:orientation val="minMax"/>
           <c:min val="0"/>
@@ -2795,7 +2795,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="10978621"/>
+        <c:crossAx val="42353931"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
         <c:majorUnit val="1"/>
@@ -2904,7 +2904,7 @@
         <xdr:cNvGraphicFramePr/>
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
-        <a:off x="7612560" y="7115040"/>
+        <a:off x="7612560" y="7257960"/>
         <a:ext cx="5759640" cy="3023640"/>
       </xdr:xfrm>
       <a:graphic>
@@ -2939,7 +2939,7 @@
         <xdr:cNvGraphicFramePr/>
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
-        <a:off x="7612560" y="7257960"/>
+        <a:off x="7612560" y="7581960"/>
         <a:ext cx="5759640" cy="3023640"/>
       </xdr:xfrm>
       <a:graphic>
@@ -4961,13 +4961,13 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="4">
+    <dataValidation allowBlank="true" error="Digite uma data no formato dia/mês/ano." errorStyle="stop" errorTitle="Data inválida" operator="greaterThanOrEqual" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="T4:T5 N11:N30" type="date">
+      <formula1>36526</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
     <dataValidation allowBlank="true" error="Digite um número inteiro de 1 a 5." errorStyle="stop" errorTitle="Nota inválida" operator="between" prompt="Número inteiro de 1 a 5, conforme a aba Escalas." promptTitle="Nota" showDropDown="false" showErrorMessage="true" showInputMessage="true" sqref="G11:H30 P11:Q30" type="whole">
       <formula1>1</formula1>
       <formula2>5</formula2>
-    </dataValidation>
-    <dataValidation allowBlank="true" error="Digite uma data no formato dia/mês/ano." errorStyle="stop" errorTitle="Data inválida" operator="greaterThanOrEqual" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="T4:T5 N11:N30" type="date">
-      <formula1>36526</formula1>
-      <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Escolha uma das opções da lista." errorStyle="stop" errorTitle="Valor inválido" operator="between" prompt="Evitar, Reduzir, Compartilhar ou Aceitar" promptTitle="Opções" showDropDown="false" showErrorMessage="true" showInputMessage="true" sqref="K11:K30" type="list">
       <formula1>"Evitar,Reduzir,Compartilhar,Aceitar"</formula1>
@@ -6168,6 +6168,10 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="4">
+    <dataValidation allowBlank="true" error="Digite uma data no formato dia/mês/ano." errorStyle="stop" errorTitle="Data inválida" operator="greaterThanOrEqual" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="L7:L16" type="date">
+      <formula1>36526</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
     <dataValidation allowBlank="true" error="Digite um número inteiro de 1 a 5." errorStyle="stop" errorTitle="Nota inválida" operator="between" prompt="Número inteiro de 1 a 5, conforme a aba Escalas." promptTitle="Nota" showDropDown="false" showErrorMessage="true" showInputMessage="true" sqref="E7:F16" type="whole">
       <formula1>1</formula1>
       <formula2>5</formula2>
@@ -6178,10 +6182,6 @@
     </dataValidation>
     <dataValidation allowBlank="true" error="Escolha uma das opções da lista." errorStyle="stop" errorTitle="Valor inválido" operator="between" prompt="Não iniciada, Em andamento ou Concluída" promptTitle="Opções" showDropDown="false" showErrorMessage="true" showInputMessage="true" sqref="M7:M16" type="list">
       <formula1>"Não iniciada,Em andamento,Concluída"</formula1>
-      <formula2>0</formula2>
-    </dataValidation>
-    <dataValidation allowBlank="true" error="Digite uma data no formato dia/mês/ano." errorStyle="stop" errorTitle="Data inválida" operator="greaterThanOrEqual" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="L7:L16" type="date">
-      <formula1>36526</formula1>
       <formula2>0</formula2>
     </dataValidation>
   </dataValidations>
@@ -7386,7 +7386,7 @@
         <v>Baixo</v>
       </c>
     </row>
-    <row r="17" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="17" customFormat="false" ht="47.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B17" s="25" t="s">
         <v>281</v>
       </c>
@@ -7417,7 +7417,7 @@
         <v>Alto</v>
       </c>
       <c r="K17" s="55" t="s">
-        <v>215</v>
+        <v>112</v>
       </c>
       <c r="L17" s="7" t="s">
         <v>285</v>
@@ -8445,7 +8445,7 @@
         <v>Baixo</v>
       </c>
     </row>
-    <row r="18" customFormat="false" ht="47.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="18" customFormat="false" ht="72.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B18" s="25" t="s">
         <v>338</v>
       </c>
